--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486417_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486417_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9203</v>
+        <v>3.8674</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5801</v>
+        <v>2.8663</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3402</v>
+        <v>1.0011</v>
       </c>
       <c r="G2" t="n">
         <v>1.5108</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>1.627</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5312</v>
+        <v>-0.1826</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0958</v>
+        <v>0.7568</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1764</v>
+        <v>3.4221</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0909</v>
+        <v>2.9359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.4862</v>
       </c>
       <c r="G3" t="n">
         <v>4.6405</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0068</v>
+        <v>0.2388</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2139</v>
+        <v>-0.3689</v>
       </c>
       <c r="U3" t="n">
-        <v>0.207</v>
+        <v>0.6077</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3698</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.06</v>
+        <v>1.6436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9176</v>
+        <v>2.4841</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1423</v>
+        <v>-0.8405</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4317</v>
+        <v>3.7089</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4507</v>
+        <v>-0.736</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9809</v>
+        <v>4.4449</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0923</v>
+        <v>3.3696</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9011</v>
+        <v>-0.2857</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1912</v>
+        <v>3.6552</v>
       </c>
       <c r="M4" t="n">
         <v>0.3393</v>
@@ -757,37 +757,37 @@
         <v>0.7897</v>
       </c>
       <c r="P4" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9334</v>
+        <v>-0.435</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8051</v>
+        <v>-0.1454</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1282</v>
+        <v>-0.2896</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2738</v>
+        <v>1.4087</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4841</v>
+        <v>0.3589</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2104</v>
+        <v>1.0498</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7089</v>
+        <v>2.4317</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.736</v>
+        <v>1.4507</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4449</v>
+        <v>0.9809</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3696</v>
+        <v>2.0923</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2857</v>
+        <v>1.9011</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6552</v>
+        <v>0.1912</v>
       </c>
       <c r="M5" t="n">
         <v>0.3393</v>
@@ -835,37 +835,37 @@
         <v>0.7897</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.2821</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1454</v>
+        <v>0.2464</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6595</v>
+        <v>0.0357</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>C. LUTETE IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.827</v>
+        <v>0.6687</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3356</v>
+        <v>-0.9005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4914</v>
+        <v>1.5692</v>
       </c>
       <c r="G6" t="n">
-        <v>0.724</v>
+        <v>1.0352</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2283</v>
+        <v>-0.3194</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4956</v>
+        <v>1.3547</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2172</v>
+        <v>0.264</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0643</v>
+        <v>-0.5991</v>
       </c>
       <c r="L6" t="n">
-        <v>0.153</v>
+        <v>0.863</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5067</v>
+        <v>0.7713</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1641</v>
+        <v>0.2796</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3426</v>
+        <v>0.4916</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8203</v>
+        <v>0.286</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0769</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8972</v>
+        <v>0.3629</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. LUTETE IV</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5454</v>
+        <v>0.2837</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9005</v>
+        <v>0.2238</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4459</v>
+        <v>0.0599</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0352</v>
+        <v>0.724</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3194</v>
+        <v>0.2283</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3547</v>
+        <v>0.4956</v>
       </c>
       <c r="J7" t="n">
-        <v>0.264</v>
+        <v>0.2172</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5991</v>
+        <v>0.0643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.863</v>
+        <v>0.153</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7713</v>
+        <v>0.5067</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2796</v>
+        <v>0.1641</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4916</v>
+        <v>0.3426</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1627</v>
+        <v>0.277</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0769</v>
+        <v>-0.1887</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2396</v>
+        <v>0.4656</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6587</v>
+        <v>-0.4853</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4797</v>
+        <v>0.5914</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1383</v>
+        <v>-1.0767</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3523</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0411</v>
+        <v>0.2145</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5649999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0585</v>
+        <v>-0.9166</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9316</v>
+        <v>-4.0808</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8732</v>
+        <v>3.1642</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2268</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3308</v>
+        <v>-0.189</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3014</v>
+        <v>-0.4506</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9706</v>
+        <v>0.2616</v>
       </c>
       <c r="V9" t="n">
         <v>1.6743</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3437</v>
+        <v>-1.0063</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.031</v>
+        <v>-1.977</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3126</v>
+        <v>0.9707</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9755</v>
+        <v>-0.4615</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3133</v>
+        <v>-0.3834</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6622</v>
+        <v>-0.0781</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6886</v>
+        <v>0.3316</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7268</v>
+        <v>0.3499</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>-0.0183</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2869</v>
+        <v>-0.7931</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4136</v>
+        <v>-0.7333</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7004</v>
+        <v>-0.0598</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3682</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3425</v>
+        <v>-0.3064</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0257</v>
+        <v>0.2412</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6759</v>
+        <v>-1.0749</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4925</v>
+        <v>-0.8546</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8166</v>
+        <v>-0.2204</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4615</v>
+        <v>-1.357</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3834</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0781</v>
+        <v>-2.3515</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3316</v>
+        <v>0.4457</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3499</v>
+        <v>1.9923</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0183</v>
+        <v>-1.5467</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7931</v>
+        <v>-1.8027</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7333</v>
+        <v>-0.9978</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0598</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7348</v>
+        <v>-0.1529</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.822</v>
+        <v>-0.2127</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0871</v>
+        <v>0.0598</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7561</v>
+        <v>-1.1587</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2583</v>
+        <v>-1.031</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4978</v>
+        <v>-0.1277</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.357</v>
+        <v>-0.9755</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9945000000000001</v>
+        <v>-0.3133</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3515</v>
+        <v>-0.6622</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4457</v>
+        <v>-0.6886</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9923</v>
+        <v>-0.7268</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5467</v>
+        <v>0.0382</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8027</v>
+        <v>-0.2869</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9978</v>
+        <v>0.4136</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.7004</v>
       </c>
       <c r="P12" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8341</v>
+        <v>-0.1833</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6165</v>
+        <v>-0.3425</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2176</v>
+        <v>0.1592</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.309999999999999</v>
+        <v>6.6524</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2740999999999996</v>
+        <v>0.6164999999999987</v>
       </c>
       <c r="F13" t="n">
-        <v>6.036</v>
+        <v>6.035800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>10.678</v>
@@ -1468,13 +1468,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5049000000000005</v>
+        <v>0.8471</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2592</v>
+        <v>-1.9165</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7638</v>
+        <v>2.7636</v>
       </c>
       <c r="V13" t="n">
         <v>0.5649999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. IDEHEN IDEHEN</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5761</v>
+        <v>4.8343</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8463</v>
+        <v>3.4149</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7298</v>
+        <v>1.4194</v>
       </c>
       <c r="G14" t="n">
-        <v>1.717</v>
+        <v>3.1708</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0213</v>
+        <v>1.0217</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6957</v>
+        <v>2.1492</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7785</v>
+        <v>3.779</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9371</v>
+        <v>1.0585</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8415</v>
+        <v>2.7205</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0616</v>
+        <v>-0.6082</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.0368</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8542</v>
+        <v>-0.5714</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2284</v>
+        <v>0.3362</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6343</v>
+        <v>-0.1466</v>
       </c>
       <c r="U14" t="n">
-        <v>1.594</v>
+        <v>0.4828</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5443</v>
+        <v>-0.1952</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-0.1952</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>E. IDEHEN IDEHEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3219</v>
+        <v>4.2409</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3032</v>
+        <v>1.2817</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0187</v>
+        <v>2.9592</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1708</v>
+        <v>1.717</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0217</v>
+        <v>0.0213</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1492</v>
+        <v>1.6957</v>
       </c>
       <c r="J15" t="n">
-        <v>3.779</v>
+        <v>1.7785</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0585</v>
+        <v>0.9371</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7205</v>
+        <v>0.8415</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6082</v>
+        <v>-0.0616</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0368</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5714</v>
+        <v>0.8542</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1763</v>
+        <v>0.8932</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2584</v>
+        <v>0.0697</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.8234</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>-0.5443</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1952</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9716</v>
+        <v>2.0833</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.9772</v>
       </c>
       <c r="F16" t="n">
         <v>1.1062</v>
@@ -1702,10 +1702,10 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.4482</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.6862</v>
       </c>
       <c r="U16" t="n">
         <v>0.2379</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1393</v>
+        <v>-0.1701</v>
       </c>
       <c r="E17" t="n">
         <v>0.8933</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0326</v>
+        <v>-1.0634</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3331</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1335</v>
+        <v>-0.1643</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2019</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0684</v>
+        <v>0.0375</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7572</v>
+        <v>-0.5645</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7076</v>
+        <v>-1.484</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9503</v>
+        <v>0.9195</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0449</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1696</v>
+        <v>0.0231</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3869</v>
+        <v>-0.1634</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2174</v>
+        <v>0.1866</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7555</v>
+        <v>-1.2776</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7309</v>
+        <v>-2.2839</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9755</v>
+        <v>1.0063</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2878</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4024</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2825</v>
+        <v>0.3133</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0774</v>
+        <v>-3.0581</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4663</v>
+        <v>-1.3546</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6111</v>
+        <v>-1.7035</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0087</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1986</v>
+        <v>-0.1794</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1318</v>
+        <v>0.0394</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5059</v>
+        <v>-3.1629</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3026</v>
+        <v>-2.7439</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2033</v>
+        <v>-0.4191</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9183</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7399</v>
+        <v>-0.3969</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2894</v>
+        <v>-0.7306</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5495</v>
+        <v>0.3338</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9222</v>
+        <v>-3.2672</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3948</v>
+        <v>-1.1713</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5274</v>
+        <v>-2.0959</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9504</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6472</v>
+        <v>0.0078</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2584</v>
+        <v>-0.0348</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3889</v>
+        <v>0.0427</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0647</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.022</v>
+        <v>-5.9681</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3418</v>
+        <v>-3.5653</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6803</v>
+        <v>-2.4029</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2067</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7055</v>
+        <v>-0.6516</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1899</v>
+        <v>-0.4134</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5157</v>
+        <v>-0.2382</v>
       </c>
       <c r="V23" t="n">
         <v>0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.309900000000001</v>
+        <v>-6.310000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0358</v>
+        <v>-6.0359</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2741999999999996</v>
+        <v>-0.2741999999999991</v>
       </c>
       <c r="G24" t="n">
         <v>-10.678</v>
@@ -2326,13 +2326,13 @@
         <v>14.138</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5045999999999999</v>
+        <v>-0.5047</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.764</v>
+        <v>-2.7638</v>
       </c>
       <c r="U24" t="n">
-        <v>2.259</v>
+        <v>2.2592</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5649</v>
